--- a/02_TRAVAIL/Lot6c_MenagesExternes/MASTER_FACT_MEN_MenagesExternes.xlsx
+++ b/02_TRAVAIL/Lot6c_MenagesExternes/MASTER_FACT_MEN_MenagesExternes.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>20260609_170942</t>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AW2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792605</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -2341,19 +2341,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP3" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP3" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ3" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS3" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AW3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792662</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2548,19 +2548,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP4" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP4" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ4" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS4" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AW4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792696</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2755,19 +2755,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP5" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP5" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ5" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS5" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AW5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792725</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2962,19 +2962,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP6" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP6" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ6" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR6" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS6" s="2" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="AW6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792753</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3169,19 +3169,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP7" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP7" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ7" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS7" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AW7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792779</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AW8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792809</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AW9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792836</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AW10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792860</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -3991,19 +3991,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP11" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP11" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ11" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR11" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS11" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="AW11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792887</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -4198,19 +4198,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP12" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP12" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ12" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR12" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS12" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="AW12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792912</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="AR13" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_MONTANT_NUL</t>
         </is>
       </c>
       <c r="AS13" s="2" t="inlineStr">
         <is>
-          <t>Ligne 3 fac.0003 — 0 ménage, logement inactif depuis 2026-04-26. Présent à 0€. | MENAGE_EXTERNE_MONTANT_NUL | MENAGE_EXTERNE_LOGEMENT_INACTIF</t>
+          <t>Ligne 3 fac.0003 — 0 ménage, logement inactif depuis 2026-04-26. Présent à 0€. | MENAGE_EXTERNE_LOGEMENT_INACTIF</t>
         </is>
       </c>
       <c r="AT13" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AW13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792943</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -4612,19 +4612,19 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="AP14" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
+      <c r="AP14" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
         </is>
       </c>
       <c r="AQ14" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="AR14" s="2" t="inlineStr">
         <is>
-          <t>MENAGE_EXTERNE_DATE_ABSENTE</t>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
         </is>
       </c>
       <c r="AS14" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="AW14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792972</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -5166,19 +5166,19 @@
       </c>
       <c r="AW2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792605</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MENEXT-2026-05-AISSATA-007</t>
+          <t>MENEXT-2026-05-AISSATA-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>50b0e9564cac93a3</t>
+          <t>a22f230949386e2b</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5189,12 +5189,10 @@
       <c r="D3" s="3" t="n">
         <v>46173</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>46165</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>DATE_PRECISE</t>
+          <t>MOIS_FACTURE</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -5212,7 +5210,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -5237,20 +5235,20 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>LOG_0009</t>
+          <t>LOG_0012</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>PROP_0003</t>
+          <t>PROP_0009</t>
         </is>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>556954</v>
+        <v>480136</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>T3 4 rue engalières</t>
+          <t>studio - cote pavé (François)</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -5259,7 +5257,7 @@
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
@@ -5267,7 +5265,7 @@
         </is>
       </c>
       <c r="V3" s="2" t="n">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="W3" s="2" t="n">
         <v>0</v>
@@ -5276,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="Z3" s="2" t="n">
         <v>1439</v>
@@ -5348,10 +5346,14 @@
           <t>INFO</t>
         </is>
       </c>
-      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
       <c r="AS3" s="2" t="inlineStr">
         <is>
-          <t>Ligne 7 fac.2026-37 — date précise sur facture</t>
+          <t>Ligne 2 fac.2026-37 — 5 passages mai 2026, date absente</t>
         </is>
       </c>
       <c r="AT3" s="2" t="inlineStr">
@@ -5366,24 +5368,24 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>MENEXT-2026-05-AISSATA-007</t>
+          <t>MENEXT-2026-05-AISSATA-002</t>
         </is>
       </c>
       <c r="AW3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792662</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MENEXT-2026-05-AISSATA-008</t>
+          <t>MENEXT-2026-05-AISSATA-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>08bd1f15a518a353</t>
+          <t>b8a07a5da3d88602</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5394,12 +5396,10 @@
       <c r="D4" s="3" t="n">
         <v>46173</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>46145</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>DATE_PRECISE</t>
+          <t>MOIS_FACTURE</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -5442,20 +5442,20 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>LOG_0016</t>
+          <t>LOG_0006</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>PROP_0012</t>
+          <t>PROP_0006</t>
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>515523</v>
+        <v>487144</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>T3 20 rue l'Amiral Galache</t>
+          <t>studio Puits verts (Caroline)</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="V4" s="2" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="Z4" s="2" t="n">
         <v>1439</v>
@@ -5553,10 +5553,14 @@
           <t>INFO</t>
         </is>
       </c>
-      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
       <c r="AS4" s="2" t="inlineStr">
         <is>
-          <t>Ligne 8a — splittée (2 dates). Facture: T3, REF: T2 (LOG_0016). Prix 55€ tarif T3 Aissata.</t>
+          <t>Ligne 3 fac.2026-37 — 10 passages mai 2026, date absente</t>
         </is>
       </c>
       <c r="AT4" s="2" t="inlineStr">
@@ -5571,24 +5575,24 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>MENEXT-2026-05-AISSATA-008</t>
+          <t>MENEXT-2026-05-AISSATA-003</t>
         </is>
       </c>
       <c r="AW4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T17:09:43.386735</t>
+          <t>2026-06-16T10:32:32.792696</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MENEXT-2026-05-AISSATA-009</t>
+          <t>MENEXT-2026-05-AISSATA-004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9eebf25b348dcc7b</t>
+          <t>f4cf91af6be072c1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5599,12 +5603,10 @@
       <c r="D5" s="3" t="n">
         <v>46173</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>46152</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>DATE_PRECISE</t>
+          <t>MOIS_FACTURE</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5622,7 +5624,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>lot6c_menages_externes.py — 20260609_170942</t>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -5647,20 +5649,20 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>LOG_0016</t>
+          <t>LOG_0011</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>PROP_0012</t>
+          <t>PROP_0008</t>
         </is>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>515523</v>
+        <v>480139</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>T3 20 rue l'Amiral Galache</t>
+          <t>T3 310 muret (David)</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -5669,7 +5671,7 @@
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
@@ -5677,7 +5679,7 @@
         </is>
       </c>
       <c r="V5" s="2" t="n">
-        <v>55</v>
+        <v>440</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>0</v>
@@ -5686,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>55</v>
+        <v>440</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>1439</v>
@@ -5758,30 +5760,1684 @@
           <t>INFO</t>
         </is>
       </c>
-      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
       <c r="AS5" s="2" t="inlineStr">
         <is>
+          <t>Ligne 4 fac.2026-37 — 8 passages mai 2026, date absente</t>
+        </is>
+      </c>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU5" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-004</t>
+        </is>
+      </c>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792725</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>55407f67703179a3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-AISSATA-001</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>MOIS_FACTURE</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Aissata.pdf</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>INT_0004</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>480142</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>studio st Pierre (Florane)</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>VIREMENT</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="n"/>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN6" s="2" t="n"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP6" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ6" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
+      <c r="AS6" s="2" t="inlineStr">
+        <is>
+          <t>Ligne 5 fac.2026-37 — 2 passages mai 2026, date absente</t>
+        </is>
+      </c>
+      <c r="AT6" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU6" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-005</t>
+        </is>
+      </c>
+      <c r="AW6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792753</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>155cc9414bbc04fa</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-AISSATA-001</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>MOIS_FACTURE</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Aissata.pdf</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>INT_0004</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0007</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0007</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>491496</v>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>T2 9 rue du Toul</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AE7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>VIREMENT</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="n"/>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL7" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="n"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP7" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ7" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR7" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
+      <c r="AS7" s="2" t="inlineStr">
+        <is>
+          <t>Ligne 6 fac.2026-37 — 8 passages mai 2026, date absente</t>
+        </is>
+      </c>
+      <c r="AT7" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU7" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV7" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-006</t>
+        </is>
+      </c>
+      <c r="AW7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792779</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>50b0e9564cac93a3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-AISSATA-001</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>DATE_PRECISE</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Aissata.pdf</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>INT_0004</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0009</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>556954</v>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>T3 4 rue engalières</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>VIREMENT</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="n"/>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="n"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP8" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ8" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr">
+        <is>
+          <t>Ligne 7 fac.2026-37 — date précise sur facture</t>
+        </is>
+      </c>
+      <c r="AT8" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU8" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV8" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-007</t>
+        </is>
+      </c>
+      <c r="AW8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792809</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>08bd1f15a518a353</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-AISSATA-001</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>DATE_PRECISE</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Aissata.pdf</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>INT_0004</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0016</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0012</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>515523</v>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>T3 20 rue l'Amiral Galache</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>VIREMENT</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="n"/>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="n"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP9" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ9" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr">
+        <is>
+          <t>Ligne 8a — splittée (2 dates). Facture: T3, REF: T2 (LOG_0016). Prix 55€ tarif T3 Aissata.</t>
+        </is>
+      </c>
+      <c r="AT9" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU9" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV9" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-008</t>
+        </is>
+      </c>
+      <c r="AW9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792836</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-AISSATA-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>9eebf25b348dcc7b</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-AISSATA-001</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>DATE_PRECISE</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Aissata.pdf</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>INT_0004</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0016</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0012</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>515523</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>T3 20 rue l'Amiral Galache</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>VIREMENT</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="n"/>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN10" s="2" t="n"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP10" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ10" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr">
+        <is>
           <t>Ligne 8b — splittée (2 dates). Facture: T3, REF: T2 (LOG_0016). Prix 55€ tarif T3 Aissata.</t>
         </is>
       </c>
-      <c r="AT5" s="2" t="inlineStr">
+      <c r="AT10" s="2" t="inlineStr">
         <is>
           <t>MENAGES_EXTERNES</t>
         </is>
       </c>
-      <c r="AU5" s="2" t="inlineStr">
+      <c r="AU10" s="2" t="inlineStr">
         <is>
           <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
         </is>
       </c>
-      <c r="AV5" s="2" t="inlineStr">
+      <c r="AV10" s="2" t="inlineStr">
         <is>
           <t>MENEXT-2026-05-AISSATA-009</t>
         </is>
       </c>
-      <c r="AW5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09T17:09:43.386735</t>
+      <c r="AW10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792860</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-MOUNIR-001</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>0c5aacd684a07bdf</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-MOUNIR-001</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>MOIS_FACTURE</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Mounir.pdf</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>INT_0003</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Mounir</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0002</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>481903</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>T.4-90 Blagnac (Cédrine)</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="n"/>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL11" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM11" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN11" s="2" t="n"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP11" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ11" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR11" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
+      <c r="AS11" s="2" t="inlineStr">
+        <is>
+          <t>Ligne 1 fac.0003 — 6 ménages mai 2026, date absente</t>
+        </is>
+      </c>
+      <c r="AT11" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU11" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV11" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-MOUNIR-001</t>
+        </is>
+      </c>
+      <c r="AW11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792887</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-MOUNIR-002</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>49338b5790100f38</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-MOUNIR-001</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>MOIS_FACTURE</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Mounir.pdf</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>INT_0003</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Mounir</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0013</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>480137</v>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>T.3 Sept Deniers (François)</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="n"/>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="n"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP12" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ12" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR12" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
+      <c r="AS12" s="2" t="inlineStr">
+        <is>
+          <t>Ligne 2 fac.0003 — 10 ménages mai 2026, date absente</t>
+        </is>
+      </c>
+      <c r="AT12" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU12" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV12" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-MOUNIR-002</t>
+        </is>
+      </c>
+      <c r="AW12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792912</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-MOUNIR-004</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>188950b5e6265b63</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FAC-2026-05-MOUNIR-001</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>MOIS_FACTURE</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Facture mai Mounir.pdf</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>lot6c_menages_externes.py — 20260616_103232</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>INT_0003</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Mounir</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>FRANCHISE_TVA</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>487144</v>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Studio Puits vert (Caroline)</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>TLM_001</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="n"/>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_014</t>
+        </is>
+      </c>
+      <c r="AM13" s="2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="AN13" s="2" t="n"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AP13" s="5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AQ13" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AR13" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_DATE_MOIS</t>
+        </is>
+      </c>
+      <c r="AS13" s="2" t="inlineStr">
+        <is>
+          <t>Ligne 4 fac.0003 — 1 ménage mai 2026, date absente</t>
+        </is>
+      </c>
+      <c r="AT13" s="2" t="inlineStr">
+        <is>
+          <t>MENAGES_EXTERNES</t>
+        </is>
+      </c>
+      <c r="AU13" s="2" t="inlineStr">
+        <is>
+          <t>MASTER_FACT_MEN_MenagesExternes.SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AV13" s="2" t="inlineStr">
+        <is>
+          <t>MENEXT-2026-05-MOUNIR-004</t>
+        </is>
+      </c>
+      <c r="AW13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T10:32:32.792972</t>
         </is>
       </c>
     </row>
@@ -5796,18 +7452,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5828,39 +7486,49 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>nb_menages_hostaway_realises</t>
+          <t>prestataires_factures</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>nb_menages_externes_factures</t>
+          <t>nombre_menages_facture</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ecart_hostaway_externe</t>
+          <t>nombre_menages_hostaway</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>statut_controle</t>
+          <t>ecart</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>niveau_anomalie</t>
+          <t>code_controle</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>code_anomalie</t>
+          <t>niveau_controle</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>commentaire_controle</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>date_actualisation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5873,35 +7541,41 @@
           <t>PROP_0001</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -5914,35 +7588,41 @@
           <t>PROP_0002</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>-6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5955,560 +7635,4355 @@
           <t>PROP_0003</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>VALIDE</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LOG_0005</t>
+          <t>LOG_0008</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PROP_0005</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>7</v>
-      </c>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>-7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>LOG_0006</t>
+          <t>LOG_0010</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PROP_0006</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>11</v>
-      </c>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>-2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>LOG_0007</t>
+          <t>LOG_0011</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PROP_0007</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>8</v>
-      </c>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>-7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LOG_0008</t>
+          <t>LOG_0012</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PROP_0008</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>5</v>
-      </c>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>-5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>LOG_0009</t>
+          <t>LOG_0013</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PROP_0003</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>-6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LOG_0010</t>
+          <t>LOG_0014</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PROP_0005</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>-5</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>LOG_0011</t>
+          <t>LOG_0001</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PROP_0008</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>9</v>
-      </c>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>-8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LOG_0012</t>
+          <t>LOG_0002</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PROP_0009</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>5</v>
-      </c>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>-9</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LOG_0013</t>
+          <t>LOG_0003</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PROP_0009</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>9</v>
-      </c>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-7</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LOG_0014</t>
+          <t>LOG_0005</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PROP_0010</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>10</v>
-      </c>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>-8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>LOG_0015</t>
+          <t>LOG_0006</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PROP_0011</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>4</v>
-      </c>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>-9</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LOG_0016</t>
+          <t>LOG_0007</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PROP_0012</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>PROP_0007</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>A_CONTROLER</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>-3</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>A_CONTROLER</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>MENAGE_EXTERNE_FACTURATION_SANS_COMPTAGE_HA</t>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0011</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0012</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0013</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0017</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0002</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0003</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0007</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0007</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0011</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0012</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0013</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0017</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0002</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Mounir</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_RAPPROCHE_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Volume facture = volume Hostaway. Rapproche ; date jour non requise.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0003</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Mounir</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Aissata,Mounir</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_RAPPROCHE_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Volume facture = volume Hostaway. Rapproche ; date jour non requise.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0007</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0007</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_RAPPROCHE_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Volume facture = volume Hostaway. Rapproche ; date jour non requise.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0009</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_LOGEMENT_HORS_HA</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Logement facture absent du comptage Hostaway (archive/hors HA/mapping). A valider, pas une erreur prestataire.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_ECART_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Ecart volume facture vs Hostaway. A valider (interne, hors HA, decalage mois ou saisie).</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0011</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_ECART_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Ecart volume facture vs Hostaway. A valider (interne, hors HA, decalage mois ou saisie).</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0012</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_RAPPROCHE_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Volume facture = volume Hostaway. Rapproche ; date jour non requise.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0013</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Mounir</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_ECART_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Ecart volume facture vs Hostaway. A valider (interne, hors HA, decalage mois ou saisie).</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_ECART_HOSTAWAY</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Ecart volume facture vs Hostaway. A valider (interne, hors HA, decalage mois ou saisie).</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0016</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0012</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Aissata</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_EXTERNE_LOGEMENT_HORS_HA</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>A_CONTROLER</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Logement facture absent du comptage Hostaway (archive/hors HA/mapping). A valider, pas une erreur prestataire.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>LOG_0017</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>PROP_0008</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>VALIDE</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>NOTE : VUE_ACTIVE ne contient que les lignes VALIDE. Les lignes A_CONTROLER (dates absentes) ne sont pas comptées dans nb_menages_externes_factures.</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0002</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0003</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0007</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0007</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0011</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0012</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0013</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>MENAGE_HA_SANS_FACTURE_EXTERNE</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Menages Hostaway sans facture externe : probable menage interne / a croiser avec M04.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0017</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0002</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0007</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0007</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0011</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0012</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0013</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0017</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0002</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0011</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0013</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0017</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0017</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0017</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0011</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Aucune activite menage ce mois.</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>20260616_103232</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>NOTE : rapprochement mensuel mois x logement, recalcule a chaque relance. nombre_menages_facture compte TOUTES les lignes facture exploitables (y compris mensuelles MOIS_FACTURE), pas seulement VALIDE. Codes neutres (rapproche / ecart / HA sans facture / logement hors HA) : un ecart signale une verification, jamais une accusation prestataire.</t>
         </is>
       </c>
     </row>
@@ -6759,7 +12234,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Généré le 20260609_170942 par lot6c_menages_externes.py</t>
+          <t>Généré le 20260616_103232 par lot6c_menages_externes.py</t>
         </is>
       </c>
     </row>
@@ -6821,14 +12296,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - VUE_ACTIVE       : 4 lignes (filtre VALIDE + IC/HC + montant&gt;0 + réconcilié)</t>
+          <t xml:space="preserve">  - VUE_ACTIVE       : 12 lignes (filtre VALIDE + IC/HC + montant&gt;0 + réconcilié)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - VUE_ECART_HA     : 16 logements — comparaison HA vs externes mai 2026</t>
+          <t xml:space="preserve">  - VUE_ECART_HA     : 97 logements — comparaison HA vs externes mai 2026</t>
         </is>
       </c>
     </row>
